--- a/docs/tableau_competences.xlsx
+++ b/docs/tableau_competences.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="xoKHdZRVz7axMqB+UK46Y1ynB1FX2Ln+dqWfQvcGnAM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ML0g1Q52+rarlMw0nGKhAiXFH/reyAZPETXIPQuk7dE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -45,7 +45,24 @@
     <t xml:space="preserve"> SLAM</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio :</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <sz val="18.0"/>
+      </rPr>
+      <t xml:space="preserve">Adresse URL du portfolio : </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FF1155CC"/>
+        <sz val="18.0"/>
+        <u/>
+      </rPr>
+      <t>https://kayzmat.github.io/Portfolio/</t>
+    </r>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -172,6 +189,9 @@
     <t>Création d'une application</t>
   </si>
   <si>
+    <t>12/05/2025 au 25/06/2025</t>
+  </si>
+  <si>
     <t>1+3</t>
   </si>
   <si>
@@ -190,14 +210,59 @@
     <t>Améliorations écran de ligne</t>
   </si>
   <si>
+    <t>PPE 3 : Application de gestion pour une auto-école fictive</t>
+  </si>
+  <si>
+    <t>Création et alimentation de la base de données</t>
+  </si>
+  <si>
+    <t>05/09/2025 au 19/09/2025</t>
+  </si>
+  <si>
+    <t>Réalisation d'une page "voiture" pour la gestion des voitures de l'auto-école</t>
+  </si>
+  <si>
+    <t>PPE 4 : Application de gestion d'évênement sportif (triathlon)</t>
+  </si>
+  <si>
+    <t>Réalisation d'un cahier des charges</t>
+  </si>
+  <si>
+    <t>03/10/2025 au 07/11/2025</t>
+  </si>
+  <si>
+    <t>Réalisation d'un schéma de navigation</t>
+  </si>
+  <si>
+    <t>Réalisation de la partie tableau de bord et licencié du site</t>
+  </si>
+  <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
+  </si>
+  <si>
+    <t>Evolution d'une application pour intégrer de nouvelles fonctionnalités (dématérialisation checklist)</t>
+  </si>
+  <si>
+    <t>05/01/2026 au 13/02/2026</t>
+  </si>
+  <si>
+    <t>Documentation utilisateur</t>
+  </si>
+  <si>
+    <t>Documentation fonctionnalités de l'application</t>
+  </si>
+  <si>
+    <t>PPE 5 : Site et application mobile de gestion des repas d'un parc animalier</t>
+  </si>
+  <si>
+    <t>Réalisation de l'application mobile</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -220,6 +285,13 @@
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18.0"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -265,6 +337,34 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="8.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <u/>
       <sz val="8.0"/>
       <color rgb="FF0000FF"/>
@@ -277,7 +377,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,8 +402,20 @@
         <bgColor theme="6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor rgb="FF9BBB59"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="31">
+  <borders count="29">
     <border/>
     <border>
       <left style="medium">
@@ -534,112 +646,72 @@
       <left style="medium">
         <color rgb="FF494429"/>
       </left>
-      <bottom style="thin">
+      <top style="medium">
         <color rgb="FF494429"/>
-      </bottom>
+      </top>
     </border>
     <border>
-      <bottom style="thin">
+      <top style="medium">
         <color rgb="FF494429"/>
-      </bottom>
+      </top>
     </border>
     <border>
       <right style="medium">
         <color rgb="FF494429"/>
       </right>
+      <top style="medium">
+        <color rgb="FF494429"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF494429"/>
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF494429"/>
+        <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF494429"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
+        <color rgb="FF000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="53">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -672,21 +744,21 @@
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -697,91 +769,78 @@
     <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="22" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="23" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="24" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="26" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="27" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="28" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="23" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="28" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="4" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="28" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="0" fontId="13" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="28" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="25" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="25" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="28" fillId="5" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="28" fillId="4" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="28" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="28" fillId="5" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="28" fillId="5" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="28" fillId="6" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="27" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="26" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="27" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1144,451 +1203,528 @@
       <c r="A8" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="6"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" ht="39.75" customHeight="1">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="28"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="30"/>
     </row>
     <row r="10" ht="39.75" customHeight="1">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="33">
+      <c r="B10" s="32"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="35">
         <v>3.0</v>
       </c>
     </row>
     <row r="11" ht="39.75" customHeight="1">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="33" t="s">
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="35" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" ht="39.75" customHeight="1">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="30"/>
     </row>
     <row r="13" ht="39.75" customHeight="1">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="35" t="s">
         <v>32</v>
       </c>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
     </row>
     <row r="14" ht="39.75" customHeight="1">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="G14" s="37">
+      <c r="B14" s="32"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="35">
         <v>1.0</v>
       </c>
-      <c r="H14" s="40"/>
+      <c r="H14" s="34"/>
     </row>
     <row r="15" ht="39.75" customHeight="1">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="41">
+      <c r="B15" s="36"/>
+      <c r="C15" s="35">
         <v>3.0</v>
       </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
     </row>
     <row r="16" ht="39.75" customHeight="1">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="30"/>
     </row>
     <row r="17" ht="39.75" customHeight="1">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="37" t="s">
+      <c r="B17" s="32"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="36"/>
     </row>
     <row r="18" ht="39.75" customHeight="1">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="10"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30"/>
     </row>
     <row r="19" ht="39.75" customHeight="1">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="37">
+      <c r="C19" s="36"/>
+      <c r="D19" s="35">
         <v>1.0</v>
       </c>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
     </row>
     <row r="20" ht="39.75" customHeight="1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="37" t="s">
+      <c r="B20" s="32"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="G20" s="39"/>
-      <c r="H20" s="40"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
     </row>
     <row r="21" ht="39.75" customHeight="1">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="37" t="s">
+      <c r="B21" s="37"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="46"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="30"/>
     </row>
     <row r="23" ht="39.75" customHeight="1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="37" t="s">
+      <c r="B23" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="40"/>
-    </row>
-    <row r="24" ht="39.75" customHeight="1">
-      <c r="A24" s="38" t="s">
+      <c r="C23" s="34"/>
+      <c r="D23" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="40"/>
-    </row>
-    <row r="25" ht="39.75" customHeight="1">
-      <c r="A25" s="38" t="s">
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+    </row>
+    <row r="24" ht="39.75" customHeight="1">
+      <c r="A24" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="40"/>
-    </row>
-    <row r="26" ht="39.75" customHeight="1">
-      <c r="A26" s="38" t="s">
+      <c r="B24" s="37"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+    </row>
+    <row r="25" ht="39.75" customHeight="1">
+      <c r="A25" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="40"/>
-    </row>
-    <row r="27" ht="39.75" customHeight="1">
-      <c r="A27" s="38" t="s">
+      <c r="B25" s="37"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+    </row>
+    <row r="26" ht="39.75" customHeight="1">
+      <c r="A26" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B27" s="44"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="37">
+      <c r="B26" s="37"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+    </row>
+    <row r="27" ht="39.75" customHeight="1">
+      <c r="A27" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="37"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="35">
         <v>3.0</v>
       </c>
-      <c r="H27" s="40"/>
+      <c r="H27" s="34"/>
     </row>
     <row r="28" ht="39.75" customHeight="1">
-      <c r="A28" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="40"/>
-    </row>
-    <row r="29" ht="39.75" customHeight="1"/>
-    <row r="30" ht="39.75" customHeight="1">
-      <c r="A30" s="47"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
-      <c r="H30" s="40"/>
-    </row>
-    <row r="31" ht="39.75" customHeight="1">
-      <c r="A31" s="47"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="40"/>
-    </row>
-    <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="48" t="s">
+      <c r="A28" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="46"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+    </row>
+    <row r="29" ht="39.75" customHeight="1">
+      <c r="A29" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="30"/>
+    </row>
+    <row r="30" ht="39.75" customHeight="1">
+      <c r="A30" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="42"/>
+      <c r="D30" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+    </row>
+    <row r="31" ht="39.75" customHeight="1">
+      <c r="A31" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="44"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+    </row>
+    <row r="32" ht="39.75" customHeight="1">
+      <c r="A32" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="30"/>
     </row>
     <row r="33" ht="39.75" customHeight="1">
-      <c r="A33" s="47"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="40"/>
+      <c r="A33" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="34"/>
+      <c r="D33" s="35">
+        <v>1.0</v>
+      </c>
+      <c r="E33" s="46"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
     </row>
     <row r="34" ht="39.75" customHeight="1">
-      <c r="A34" s="47"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="40"/>
+      <c r="A34" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="35">
+        <v>1.0</v>
+      </c>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
     </row>
     <row r="35" ht="39.75" customHeight="1">
-      <c r="A35" s="47"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="40"/>
+      <c r="A35" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="37"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
     </row>
     <row r="36" ht="39.75" customHeight="1">
-      <c r="A36" s="47"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="40"/>
+      <c r="A36" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
     </row>
     <row r="37" ht="39.75" customHeight="1">
-      <c r="A37" s="47"/>
-      <c r="B37" s="44"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="40"/>
+      <c r="A37" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="30"/>
     </row>
     <row r="38" ht="39.75" customHeight="1">
-      <c r="A38" s="47"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="40"/>
+      <c r="A38" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="34"/>
+      <c r="D38" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
     </row>
     <row r="39" ht="39.75" customHeight="1">
-      <c r="A39" s="49"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="52"/>
-    </row>
-    <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="53"/>
-      <c r="B40" s="54"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-    </row>
-    <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-    </row>
-    <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-    </row>
-    <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-    </row>
-    <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-    </row>
-    <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="7"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-    </row>
-    <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="7"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-    </row>
+      <c r="A39" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
+    </row>
+    <row r="40" ht="39.75" customHeight="1">
+      <c r="A40" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="37"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="35">
+        <v>3.0</v>
+      </c>
+      <c r="H40" s="34"/>
+    </row>
+    <row r="41" ht="39.75" customHeight="1">
+      <c r="A41" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="37"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="35">
+        <v>3.0</v>
+      </c>
+      <c r="H41" s="34"/>
+    </row>
+    <row r="42" ht="39.75" customHeight="1">
+      <c r="A42" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="30"/>
+    </row>
+    <row r="43" ht="39.75" customHeight="1">
+      <c r="A43" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="37"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="34"/>
+    </row>
+    <row r="44" ht="39.75" customHeight="1">
+      <c r="A44" s="31"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="34"/>
+    </row>
+    <row r="45" ht="39.75" customHeight="1">
+      <c r="A45" s="31"/>
+      <c r="B45" s="37"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="34"/>
+    </row>
+    <row r="46" ht="39.75" customHeight="1"/>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="7"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
+      <c r="A47" s="50"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="7"/>
@@ -11170,8 +11306,78 @@
       <c r="G1005" s="7"/>
       <c r="H1005" s="7"/>
     </row>
+    <row r="1006" ht="12.75" customHeight="1">
+      <c r="A1006" s="7"/>
+      <c r="B1006" s="7"/>
+      <c r="C1006" s="7"/>
+      <c r="D1006" s="7"/>
+      <c r="E1006" s="7"/>
+      <c r="F1006" s="7"/>
+      <c r="G1006" s="7"/>
+      <c r="H1006" s="7"/>
+    </row>
+    <row r="1007" ht="12.75" customHeight="1">
+      <c r="A1007" s="7"/>
+      <c r="B1007" s="7"/>
+      <c r="C1007" s="7"/>
+      <c r="D1007" s="7"/>
+      <c r="E1007" s="7"/>
+      <c r="F1007" s="7"/>
+      <c r="G1007" s="7"/>
+      <c r="H1007" s="7"/>
+    </row>
+    <row r="1008" ht="12.75" customHeight="1">
+      <c r="A1008" s="7"/>
+      <c r="B1008" s="7"/>
+      <c r="C1008" s="7"/>
+      <c r="D1008" s="7"/>
+      <c r="E1008" s="7"/>
+      <c r="F1008" s="7"/>
+      <c r="G1008" s="7"/>
+      <c r="H1008" s="7"/>
+    </row>
+    <row r="1009" ht="12.75" customHeight="1">
+      <c r="A1009" s="7"/>
+      <c r="B1009" s="7"/>
+      <c r="C1009" s="7"/>
+      <c r="D1009" s="7"/>
+      <c r="E1009" s="7"/>
+      <c r="F1009" s="7"/>
+      <c r="G1009" s="7"/>
+      <c r="H1009" s="7"/>
+    </row>
+    <row r="1010" ht="12.75" customHeight="1">
+      <c r="A1010" s="7"/>
+      <c r="B1010" s="7"/>
+      <c r="C1010" s="7"/>
+      <c r="D1010" s="7"/>
+      <c r="E1010" s="7"/>
+      <c r="F1010" s="7"/>
+      <c r="G1010" s="7"/>
+      <c r="H1010" s="7"/>
+    </row>
+    <row r="1011" ht="12.75" customHeight="1">
+      <c r="A1011" s="7"/>
+      <c r="B1011" s="7"/>
+      <c r="C1011" s="7"/>
+      <c r="D1011" s="7"/>
+      <c r="E1011" s="7"/>
+      <c r="F1011" s="7"/>
+      <c r="G1011" s="7"/>
+      <c r="H1011" s="7"/>
+    </row>
+    <row r="1012" ht="12.75" customHeight="1">
+      <c r="A1012" s="7"/>
+      <c r="B1012" s="7"/>
+      <c r="C1012" s="7"/>
+      <c r="D1012" s="7"/>
+      <c r="E1012" s="7"/>
+      <c r="F1012" s="7"/>
+      <c r="G1012" s="7"/>
+      <c r="H1012" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="19">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -11180,7 +11386,10 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
@@ -11190,23 +11399,37 @@
     <mergeCell ref="A18:H18"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="H10"/>
-    <hyperlink r:id="rId2" ref="H11"/>
-    <hyperlink r:id="rId3" ref="F13"/>
-    <hyperlink r:id="rId4" ref="G14"/>
-    <hyperlink r:id="rId5" ref="C15"/>
-    <hyperlink r:id="rId6" ref="E17"/>
-    <hyperlink r:id="rId7" ref="D19"/>
-    <hyperlink r:id="rId8" ref="F20"/>
-    <hyperlink r:id="rId9" location="heading=h.x39iq4tmq8x8" ref="E21"/>
-    <hyperlink r:id="rId10" ref="D23"/>
-    <hyperlink r:id="rId11" ref="D24"/>
-    <hyperlink r:id="rId12" ref="G27"/>
-    <hyperlink r:id="rId13" ref="D28"/>
+    <hyperlink r:id="rId1" ref="A5"/>
+    <hyperlink r:id="rId2" ref="H10"/>
+    <hyperlink r:id="rId3" ref="H11"/>
+    <hyperlink r:id="rId4" ref="F13"/>
+    <hyperlink r:id="rId5" ref="G14"/>
+    <hyperlink r:id="rId6" ref="C15"/>
+    <hyperlink r:id="rId7" ref="E17"/>
+    <hyperlink r:id="rId8" ref="D19"/>
+    <hyperlink r:id="rId9" ref="F20"/>
+    <hyperlink r:id="rId10" location="heading=h.x39iq4tmq8x8" ref="E21"/>
+    <hyperlink r:id="rId11" ref="D23"/>
+    <hyperlink r:id="rId12" ref="D24"/>
+    <hyperlink r:id="rId13" ref="D25"/>
+    <hyperlink r:id="rId14" ref="D26"/>
+    <hyperlink r:id="rId15" ref="G27"/>
+    <hyperlink r:id="rId16" ref="D28"/>
+    <hyperlink r:id="rId17" ref="D30"/>
+    <hyperlink r:id="rId18" ref="E31"/>
+    <hyperlink r:id="rId19" location="heading=h.t8bf9nhrtate" ref="D33"/>
+    <hyperlink r:id="rId20" ref="F34"/>
+    <hyperlink r:id="rId21" ref="D35"/>
+    <hyperlink r:id="rId22" ref="E36"/>
+    <hyperlink r:id="rId23" ref="D38"/>
+    <hyperlink r:id="rId24" ref="D39"/>
+    <hyperlink r:id="rId25" ref="G40"/>
+    <hyperlink r:id="rId26" ref="G41"/>
+    <hyperlink r:id="rId27" ref="D43"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins bottom="0.1968503937007874" footer="0.0" header="0.0" left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId14"/>
+  <drawing r:id="rId28"/>
 </worksheet>
 </file>
--- a/docs/tableau_competences.xlsx
+++ b/docs/tableau_competences.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -30,7 +30,7 @@
     <t>NOM et prénom : Matéo Gonçalves Mota</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
+    <t>N° candidat : 02248103746</t>
   </si>
   <si>
     <t>Centre de formation :</t>
@@ -141,7 +141,7 @@
     <t>3+4</t>
   </si>
   <si>
-    <t>PPE 1.1 : Création d'un domaine windows, création de 2 postes clients connectés à ce domaine et un serveur web linux également connecté au domaine</t>
+    <t>AP 1.1 : Création d'un domaine windows, création de 2 postes clients connectés à ce domaine et un serveur web linux également connecté au domaine</t>
   </si>
   <si>
     <t>Planification des tâches</t>
@@ -159,16 +159,19 @@
     <t>Contraintes utilisateurs</t>
   </si>
   <si>
-    <t>PPE 1.2 : Création d'un site vitrine pour l'entreprise BST 79 sur wordpress</t>
+    <t>AP 1.2 : Création d'un site vitrine pour l'entreprise BST 79 sur wordpress</t>
   </si>
   <si>
     <t>Création de la page à propos</t>
   </si>
   <si>
+    <t>28/11/2024 au 16/01/2025</t>
+  </si>
+  <si>
     <t>1+2+3</t>
   </si>
   <si>
-    <t>PPE 2 : Création d'un site de réservation d'emplacement dans des salons pour l'entreprise fictive Tellis</t>
+    <t>AP 2 : Création d'un site de réservation d'emplacement dans des salons pour l'entreprise fictive Tellis</t>
   </si>
   <si>
     <t>Cahier des charges</t>
@@ -210,7 +213,7 @@
     <t>Améliorations écran de ligne</t>
   </si>
   <si>
-    <t>PPE 3 : Application de gestion pour une auto-école fictive</t>
+    <t>AP 3 : Application de gestion pour une auto-école fictive</t>
   </si>
   <si>
     <t>Création et alimentation de la base de données</t>
@@ -222,7 +225,7 @@
     <t>Réalisation d'une page "voiture" pour la gestion des voitures de l'auto-école</t>
   </si>
   <si>
-    <t>PPE 4 : Application de gestion d'évênement sportif (triathlon)</t>
+    <t>AP 4 : Application de gestion d'évênement sportif (triathlon)</t>
   </si>
   <si>
     <t>Réalisation d'un cahier des charges</t>
@@ -252,10 +255,13 @@
     <t>Documentation fonctionnalités de l'application</t>
   </si>
   <si>
-    <t>PPE 5 : Site et application mobile de gestion des repas d'un parc animalier</t>
+    <t>AP 5 : Site et application mobile de gestion des repas d'un parc animalier</t>
   </si>
   <si>
     <t>Réalisation de l'application mobile</t>
+  </si>
+  <si>
+    <t>05/12/2025 au 03/04/2026</t>
   </si>
 </sst>
 </file>
@@ -724,7 +730,7 @@
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1323,11 +1329,13 @@
       <c r="A17" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="32"/>
+      <c r="B17" s="32" t="s">
+        <v>37</v>
+      </c>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
       <c r="E17" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="34"/>
@@ -1335,7 +1343,7 @@
     </row>
     <row r="18" ht="39.75" customHeight="1">
       <c r="A18" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="29"/>
       <c r="C18" s="29"/>
@@ -1347,10 +1355,10 @@
     </row>
     <row r="19" ht="39.75" customHeight="1">
       <c r="A19" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="36"/>
       <c r="D19" s="35">
@@ -1370,20 +1378,20 @@
       <c r="D20" s="34"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G20" s="34"/>
       <c r="H20" s="34"/>
     </row>
     <row r="21" ht="39.75" customHeight="1">
       <c r="A21" s="31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="37"/>
       <c r="C21" s="34"/>
       <c r="D21" s="34"/>
       <c r="E21" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" s="34"/>
       <c r="G21" s="34"/>
@@ -1391,7 +1399,7 @@
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="29"/>
       <c r="C22" s="29"/>
@@ -1403,14 +1411,14 @@
     </row>
     <row r="23" ht="39.75" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" s="34"/>
       <c r="D23" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="34"/>
@@ -1419,12 +1427,12 @@
     </row>
     <row r="24" ht="39.75" customHeight="1">
       <c r="A24" s="31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="37"/>
       <c r="C24" s="34"/>
       <c r="D24" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
@@ -1433,12 +1441,12 @@
     </row>
     <row r="25" ht="39.75" customHeight="1">
       <c r="A25" s="31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="37"/>
       <c r="C25" s="34"/>
       <c r="D25" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="34"/>
@@ -1447,12 +1455,12 @@
     </row>
     <row r="26" ht="39.75" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" s="37"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="34"/>
@@ -1461,7 +1469,7 @@
     </row>
     <row r="27" ht="39.75" customHeight="1">
       <c r="A27" s="31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" s="37"/>
       <c r="C27" s="34"/>
@@ -1475,12 +1483,12 @@
     </row>
     <row r="28" ht="39.75" customHeight="1">
       <c r="A28" s="31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" s="37"/>
       <c r="C28" s="34"/>
       <c r="D28" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" s="34"/>
       <c r="F28" s="34"/>
@@ -1489,7 +1497,7 @@
     </row>
     <row r="29" ht="39.75" customHeight="1">
       <c r="A29" s="39" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
@@ -1501,10 +1509,10 @@
     </row>
     <row r="30" ht="39.75" customHeight="1">
       <c r="A30" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B30" s="41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="42"/>
       <c r="D30" s="43" t="s">
@@ -1517,13 +1525,13 @@
     </row>
     <row r="31" ht="39.75" customHeight="1">
       <c r="A31" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B31" s="44"/>
       <c r="C31" s="42"/>
       <c r="D31" s="42"/>
       <c r="E31" s="45" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" s="42"/>
       <c r="G31" s="42"/>
@@ -1531,7 +1539,7 @@
     </row>
     <row r="32" ht="39.75" customHeight="1">
       <c r="A32" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B32" s="29"/>
       <c r="C32" s="29"/>
@@ -1543,10 +1551,10 @@
     </row>
     <row r="33" ht="39.75" customHeight="1">
       <c r="A33" s="31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C33" s="34"/>
       <c r="D33" s="35">
@@ -1559,7 +1567,7 @@
     </row>
     <row r="34" ht="39.75" customHeight="1">
       <c r="A34" s="31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" s="37"/>
       <c r="C34" s="34"/>
@@ -1573,7 +1581,7 @@
     </row>
     <row r="35" ht="39.75" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35" s="37"/>
       <c r="C35" s="34"/>
@@ -1587,13 +1595,13 @@
     </row>
     <row r="36" ht="39.75" customHeight="1">
       <c r="A36" s="31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36" s="36"/>
       <c r="C36" s="36"/>
       <c r="D36" s="36"/>
       <c r="E36" s="35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F36" s="36"/>
       <c r="G36" s="36"/>
@@ -1601,7 +1609,7 @@
     </row>
     <row r="37" ht="39.75" customHeight="1">
       <c r="A37" s="38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
@@ -1613,14 +1621,14 @@
     </row>
     <row r="38" ht="39.75" customHeight="1">
       <c r="A38" s="31" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B38" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C38" s="34"/>
       <c r="D38" s="47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="34"/>
@@ -1629,12 +1637,12 @@
     </row>
     <row r="39" ht="39.75" customHeight="1">
       <c r="A39" s="31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
       <c r="D39" s="48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E39" s="37"/>
       <c r="F39" s="37"/>
@@ -1643,7 +1651,7 @@
     </row>
     <row r="40" ht="39.75" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B40" s="37"/>
       <c r="C40" s="34"/>
@@ -1657,7 +1665,7 @@
     </row>
     <row r="41" ht="39.75" customHeight="1">
       <c r="A41" s="31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B41" s="37"/>
       <c r="C41" s="34"/>
@@ -1671,7 +1679,7 @@
     </row>
     <row r="42" ht="39.75" customHeight="1">
       <c r="A42" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
@@ -1683,9 +1691,11 @@
     </row>
     <row r="43" ht="39.75" customHeight="1">
       <c r="A43" s="31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
-      <c r="B43" s="37"/>
+      <c r="B43" s="32" t="s">
+        <v>69</v>
+      </c>
       <c r="C43" s="34"/>
       <c r="D43" s="35" t="s">
         <v>32</v>
